--- a/decks/party-kids-america/keyword-research.xlsx
+++ b/decks/party-kids-america/keyword-research.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,13 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +58,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008CC53F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0046AE41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e67e22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002980b9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00c0392b"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -92,6 +122,27 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,57 +525,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Article Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Primary Keyword</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>KD Band</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -550,12 +601,12 @@
       <c r="E2" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -580,49 +631,49 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Bounce House Rental Near Me: How to Choose the Right Company</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>bounce house rental near me</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
         <v>27100</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Highest-volume keyword in category.</t>
         </is>
@@ -648,12 +699,12 @@
       <c r="E4" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -678,49 +729,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Bounce House Rentals Pearland TX: Party Kids America Guide</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>bounce house rentals pearland tx</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Primary location hub page.</t>
         </is>
@@ -746,12 +797,12 @@
       <c r="E6" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -771,49 +822,49 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>How Much Does a Bounce House Rental Cost? (Texas 2026 Guide)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>bounce house rental cost</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="3" t="n">
         <v>6600</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>GSC shows mechanical bull rental pos 22.3 — price-guide format captures comparison searchers.</t>
         </is>
@@ -839,12 +890,12 @@
       <c r="E8" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -869,49 +920,49 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Kids Party Planning Guide: How to Throw the Best Backyard Party in Houston</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>kids party ideas houston</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Pillar hub for party planning cluster.</t>
         </is>
@@ -937,12 +988,12 @@
       <c r="E10" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -967,49 +1018,48 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Inflatable Obstacle Course Rentals: Best Options for Houston Birthday Parties</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>inflatable obstacle course rental</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1031,12 +1081,12 @@
       <c r="E12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
@@ -1056,49 +1106,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>How to Set Up a Bounce House: Safety, Space, and Setup Tips</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>how to set up bounce house</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="3" t="n">
         <v>4400</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>AEO format — trust builder before they book.</t>
         </is>
@@ -1124,12 +1174,12 @@
       <c r="E14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -1149,49 +1199,48 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Bounce House Rentals Pasadena TX: Guide for Pasadena Party Planners</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>bounce house rentals pasadena tx</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1213,12 +1262,12 @@
       <c r="E16" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -1238,49 +1287,48 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Bounce House vs Inflatable Obstacle Course: Which Is Better for Kids?</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>bounce house vs obstacle course inflatable</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Compare</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1302,12 +1350,12 @@
       <c r="E18" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -1327,49 +1375,48 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Backyard Birthday Party Ideas for Kids: Houston Edition</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>backyard birthday party ideas kids houston</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1391,12 +1438,12 @@
       <c r="E20" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
@@ -1416,49 +1463,48 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Inflatable Rentals Houston TX: Full Catalog Guide for 2026</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>inflatable rentals houston tx</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1480,12 +1526,12 @@
       <c r="E22" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -1505,49 +1551,48 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Bounce House Rentals Friendswood TX: Same-Day Delivery Options</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>bounce house rentals friendswood tx</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1569,12 +1614,12 @@
       <c r="E24" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -1599,49 +1644,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Bounce House Weight Limit: What Parents Need to Know</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>bounce house weight limit</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="3" t="n">
         <v>3600</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>AEO format.</t>
         </is>
@@ -1667,12 +1712,12 @@
       <c r="E26" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -1692,49 +1737,48 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Bounce House Rentals Missouri City TX: Party Guide</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>bounce house rentals missouri city tx</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1756,12 +1800,12 @@
       <c r="E28" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
@@ -1781,49 +1825,48 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>School Carnival Rentals Houston: Games, Inflatables, and Concessions</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>school carnival rentals houston</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="n">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1845,12 +1888,12 @@
       <c r="E30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -1870,49 +1913,48 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Bounce House Rentals Stafford TX: Full Guide</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>bounce house rentals stafford tx</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="n">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1934,12 +1976,12 @@
       <c r="E32" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -1959,49 +2001,49 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>How Far in Advance Should You Book a Bounce House Rental?</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>how far in advance book bounce house</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>AEO format — common booking question.</t>
         </is>
@@ -2027,12 +2069,12 @@
       <c r="E34" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2052,49 +2094,48 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Water Slide Rentals Houston TX: Best Options for Summer 2026</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>water slide rentals houston tx</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="n">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2116,12 +2157,12 @@
       <c r="E36" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2141,49 +2182,49 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Concession Machine Rentals Houston: Popcorn, Snow Cone, Cotton Candy</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>concession machine rentals houston</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="n">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Upsell opportunity — common add-on.</t>
         </is>
@@ -2209,12 +2250,12 @@
       <c r="E38" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -2234,49 +2275,49 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Bounce House Insurance and Safety Regulations in Texas</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>bounce house rental regulations texas</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Trust content — differentiates from fly-by-night operators.</t>
         </is>
@@ -2302,12 +2343,12 @@
       <c r="E40" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2327,49 +2368,49 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Party Kids America Review: What Pearland Parents Say</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>party kids america review</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Branded</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Reputation content — captures branded review queries.</t>
         </is>
@@ -2395,12 +2436,12 @@
       <c r="E42" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -2425,49 +2466,48 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Bounce House Rentals Katy TX: Houston West Party Guide</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>bounce house rentals katy tx</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="n">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2489,12 +2529,12 @@
       <c r="E44" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2514,49 +2554,48 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Inflatable Obstacle Course Rental Near Me: Best Options in Houston</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>inflatable obstacle course rental near me</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="n">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2578,12 +2617,12 @@
       <c r="E46" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -2603,49 +2642,49 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Birthday Party Package Deals: How to Bundle and Save in Houston</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>birthday party package deals houston</t>
         </is>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="n">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Targets multi-item bookings.</t>
         </is>
@@ -2671,12 +2710,12 @@
       <c r="E48" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2696,49 +2735,48 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Bounce House Rentals Humble TX: Options for Humble Events</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>bounce house rentals humble tx</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="n">
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2760,12 +2798,12 @@
       <c r="E50" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
@@ -2790,49 +2828,49 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Water Slide Rental Safety: What to Check Before the Kids Jump In</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>water slide rental safety</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="J51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>AEO format. Trust builder.</t>
         </is>
@@ -2858,12 +2896,12 @@
       <c r="E52" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -2883,49 +2921,49 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Moonwalk Rentals Houston: What They Are and Where to Book</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>moonwalk rental houston</t>
         </is>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="n">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>'Moonwalk' is Texas slang for bounce house — captures local vernacular.</t>
         </is>
@@ -2951,12 +2989,12 @@
       <c r="E54" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -2976,49 +3014,48 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Bounce House Rentals Rosenberg TX: Fort Bend County Guide</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>bounce house rentals rosenberg tx</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="n">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3040,12 +3077,12 @@
       <c r="E56" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -3065,49 +3102,48 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>First Birthday Party Ideas: Complete Planning Guide for Houston Parents</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>first birthday party ideas houston</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J57" s="4" t="n">
+      <c r="J57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3129,12 +3165,12 @@
       <c r="E58" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -3159,49 +3195,48 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Dunk Tank Rental Houston: Pricing and What to Expect</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>dunk tank rental houston</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="n">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3223,12 +3258,12 @@
       <c r="E60" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -3248,49 +3283,48 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Bounce House Rentals Tomball TX: Northwest Houston Guide</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>bounce house rentals tomball tx</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="n">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3312,12 +3346,12 @@
       <c r="E62" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
@@ -3337,49 +3371,49 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>How to Clean and Maintain Bounce House Equipment: A Renter's Guide</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>bounce house cleaning maintenance</t>
         </is>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="J63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Trust content — shows Party Kids America's standards.</t>
         </is>
@@ -3405,12 +3439,12 @@
       <c r="E64" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -3430,49 +3464,48 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Inflatable Water Park Rental Houston: Mega Slides and Splash Pads</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>inflatable water park rental houston</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="n">
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3494,12 +3527,12 @@
       <c r="E66" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -3524,49 +3557,49 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Grad Party Rentals Houston: Ideas for High School Graduation Celebrations</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>grad party rentals houston</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="n">
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Seasonal — spring graduation bookings.</t>
         </is>
@@ -3592,12 +3625,12 @@
       <c r="E68" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -3622,49 +3655,48 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Bounce House Rentals Galveston TX: Island Party Guide</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>bounce house rentals galveston tx</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="3" t="n">
         <v>390</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="n">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3686,12 +3718,12 @@
       <c r="E70" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -3711,49 +3743,48 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Themed Bounce House Rentals Houston: Disney, Sports, Princess Options</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>themed bounce house rental houston</t>
         </is>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="n">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -3775,12 +3806,12 @@
       <c r="E72" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -3805,49 +3836,48 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Bounce House Rentals Beaumont TX: Southeast Texas Guide</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>bounce house rentals beaumont tx</t>
         </is>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="n">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -3869,12 +3899,12 @@
       <c r="E74" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -3894,49 +3924,49 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Fall Festival Inflatables Houston: October Party Planning Guide</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>fall festival inflatables houston</t>
         </is>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J75" s="4" t="n">
+      <c r="J75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Seasonal — fall bookings.</t>
         </is>
@@ -3962,12 +3992,12 @@
       <c r="E76" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -3992,49 +4022,48 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Bounce House Rentals Texas City TX: Galveston County Guide</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>bounce house rentals texas city tx</t>
         </is>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="n">
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -4056,12 +4085,12 @@
       <c r="E78" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -4086,49 +4115,48 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Bounce House Rentals Kemah TX: Waterfront Party Guide</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>bounce house rentals kemah tx</t>
         </is>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="n">
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -4150,12 +4178,12 @@
       <c r="E80" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -4180,49 +4208,48 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Bounce House Rentals Seabrook TX: Clear Lake Area Guide</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>bounce house rentals seabrook tx</t>
         </is>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="n">
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -4244,12 +4271,12 @@
       <c r="E82" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
@@ -4274,49 +4301,49 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>How Long Can You Rent a Bounce House? Hourly vs All-Day Options</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>how long bounce house rental</t>
         </is>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J83" s="4" t="n">
+      <c r="J83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K83" s="5" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>AEO format.</t>
         </is>
@@ -4342,12 +4369,12 @@
       <c r="E84" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -4367,49 +4394,49 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Foam Party Machine Rental Houston: What Is It and How It Works</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>foam party machine rental houston</t>
         </is>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="n">
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K85" s="5" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Growing trend — low competition.</t>
         </is>
@@ -4435,12 +4462,12 @@
       <c r="E86" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -4460,49 +4487,49 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Party Entertainment Ideas for Tweens: Beyond the Bounce House</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>party entertainment ideas tweens</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J87" s="4" t="n">
+      <c r="J87" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K87" s="5" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Bridges younger audience to specialty rentals.</t>
         </is>
@@ -4528,12 +4555,12 @@
       <c r="E88" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -4558,49 +4585,49 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Moonwalk Rental Pearland TX: What's the Difference from a Bounce House?</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>moonwalk rental pearland tx</t>
         </is>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="n">
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>Texas vernacular for bounce house.</t>
         </is>
@@ -4626,12 +4653,12 @@
       <c r="E90" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -4651,49 +4678,48 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Backyard Graduation Party Ideas: Inflatables for 2026 Grads</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>backyard graduation party inflatables</t>
         </is>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G91" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n">
+      <c r="J91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -4715,12 +4741,12 @@
       <c r="E92" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -4740,49 +4766,49 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>How to Plan a Perfect Kids' Birthday Party in Pearland TX</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>kids birthday party planning pearland tx</t>
         </is>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Top of funnel</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J93" s="4" t="n">
+      <c r="J93" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K93" s="5" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>Local authority content.</t>
         </is>
@@ -4808,12 +4834,12 @@
       <c r="E94" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -4833,49 +4859,49 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Water Slide Rental Summer Booking Tips: Avoid the Sold-Out Rush</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>water slide rental booking tips summer</t>
         </is>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J95" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K95" s="5" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Seasonal urgency — drives early bookings.</t>
         </is>
@@ -4901,12 +4927,12 @@
       <c r="E96" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -4931,49 +4957,49 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Party Kids America vs Other Houston Rental Companies: Honest Comparison</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>party kids america vs competitors</t>
         </is>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>Branded</t>
         </is>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J97" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K97" s="5" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>Captures decision-stage searchers comparing options.</t>
         </is>
@@ -4999,12 +5025,12 @@
       <c r="E98" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5024,49 +5050,49 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>What Size Generator Do I Need for a Bounce House?</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>generator for bounce house</t>
         </is>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="3" t="n">
         <v>2900</v>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J99" s="4" t="n">
+      <c r="J99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="5" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>AEO format — addresses a real logistical concern.</t>
         </is>
@@ -5092,12 +5118,12 @@
       <c r="E100" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5117,49 +5143,48 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Corporate Picnic Entertainment Houston: Inflatables and Games for Teams</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>corporate picnic entertainment houston</t>
         </is>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="n">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -5181,12 +5206,12 @@
       <c r="E102" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5204,52 +5229,50 @@
       <c r="J102" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Inflatable Jousting Rental Houston: Party Game Ideas</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>inflatable jousting rental houston</t>
         </is>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="3" t="n">
         <v>590</v>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="E103" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G103" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="n">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -5271,12 +5294,12 @@
       <c r="E104" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5294,52 +5317,50 @@
       <c r="J104" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Giant Slide Rental Houston: Dry Slides for Backyard Parties</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>giant slide rental houston</t>
         </is>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J105" s="4" t="n">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -5361,12 +5382,12 @@
       <c r="E106" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5384,52 +5405,50 @@
       <c r="J106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Sno-Cone Machine Rental Houston: Pricing and Booking Guide</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>snow cone machine rental houston</t>
         </is>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E107" s="4" t="n">
+      <c r="E107" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J107" s="4" t="n">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -5451,12 +5470,12 @@
       <c r="E108" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5474,52 +5493,50 @@
       <c r="J108" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Can You Rent a Bounce House for a Park? (Texas Park Rules)</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>bounce house rental park texas</t>
         </is>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E109" s="4" t="n">
+      <c r="E109" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J109" s="4" t="n">
+      <c r="J109" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -5541,12 +5558,12 @@
       <c r="E110" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5564,52 +5581,50 @@
       <c r="J110" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="n">
+      <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Dunk Tank Rental Pearland TX: Pricing and Logistics</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>dunk tank rental pearland tx</t>
         </is>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E111" s="4" t="n">
+      <c r="E111" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J111" s="4" t="n">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -5631,12 +5646,12 @@
       <c r="E112" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5654,52 +5669,50 @@
       <c r="J112" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="n">
+      <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>How to Anchor a Bounce House in Texas Wind</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>how to anchor bounce house wind</t>
         </is>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="3" t="n">
         <v>1600</v>
       </c>
-      <c r="E113" s="4" t="n">
+      <c r="E113" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J113" s="4" t="n">
+      <c r="J113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -5721,12 +5734,12 @@
       <c r="E114" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G114" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5744,52 +5757,50 @@
       <c r="J114" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="n">
+      <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Outdoor Movie Screen Rental Houston: Backyard Cinema Party Ideas</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>outdoor movie screen rental houston</t>
         </is>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E115" s="4" t="n">
+      <c r="E115" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I115" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J115" s="4" t="n">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -5811,12 +5822,12 @@
       <c r="E116" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -5834,52 +5845,50 @@
       <c r="J116" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="n">
+      <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Bounce House Rental Deposit and Cancellation Policies Explained</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>bounce house rental deposit policy</t>
         </is>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G117" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J117" s="4" t="n">
+      <c r="J117" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -5901,12 +5910,12 @@
       <c r="E118" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -5924,52 +5933,50 @@
       <c r="J118" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="n">
+      <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Bounce House Rentals Magnolia TX: Northwest Houston Party Guide</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>bounce house rentals magnolia tx</t>
         </is>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J119" s="4" t="n">
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -5991,12 +5998,12 @@
       <c r="E120" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -6014,52 +6021,50 @@
       <c r="J120" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="n">
+      <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Bounce House Delivery and Setup: What to Expect on Party Day</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>bounce house delivery setup expectations</t>
         </is>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E121" s="4" t="n">
+      <c r="E121" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="J121" s="4" t="n">
+      <c r="J121" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K121" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6086,42 +6091,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>KD Band</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Pillar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>In Plan?</t>
         </is>
@@ -6139,12 +6144,12 @@
       <c r="C2" t="n">
         <v>26</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -6166,38 +6171,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>bounce house rental houston</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" t="n">
         <v>5400</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" t="n">
         <v>24</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6215,12 +6220,12 @@
       <c r="C4" t="n">
         <v>22</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -6242,38 +6247,38 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>mechanical bull rental near me</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" t="n">
         <v>3600</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" t="n">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6291,12 +6296,12 @@
       <c r="C6" t="n">
         <v>14</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -6318,38 +6323,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>party rentals houston</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" t="n">
         <v>4400</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>22</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Party Package Planning</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6367,12 +6372,12 @@
       <c r="C8" t="n">
         <v>14</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Local Authority</t>
         </is>
@@ -6394,38 +6399,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>mechanical bull rental houston tx</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" t="n">
         <v>1600</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" t="n">
         <v>14</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6443,12 +6448,12 @@
       <c r="C10" t="n">
         <v>16</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -6470,38 +6475,38 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>bounce house permit texas</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" t="n">
         <v>1600</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6519,12 +6524,12 @@
       <c r="C12" t="n">
         <v>8</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -6546,38 +6551,38 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>do you need permit bounce house texas</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" t="n">
         <v>1600</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Middle of funnel</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6595,12 +6600,12 @@
       <c r="C14" t="n">
         <v>16</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Inflatable Rentals</t>
         </is>
@@ -6622,38 +6627,38 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>foam party machine rental houston</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" t="n">
         <v>1000</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" t="n">
         <v>10</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Bottom of funnel</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bottom of funnel</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6671,12 +6676,12 @@
       <c r="C16" t="n">
         <v>10</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Specialty Rentals</t>
         </is>
@@ -6719,27 +6724,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Monthly Searches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Reason Category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Why We Excluded It</t>
         </is>
@@ -6769,23 +6774,23 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>used bounce house for sale</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" t="n">
         <v>5400</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" t="n">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Wrong intent</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>E-commerce intent — looking to purchase used equipment.</t>
         </is>
@@ -6815,23 +6820,23 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>bounce house insurance</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" t="n">
         <v>2400</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" t="n">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Wrong audience</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Business owner research intent — targets rental operators, not event bookers.</t>
         </is>
@@ -6861,23 +6866,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>free bounce house rental</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" t="n">
         <v>1300</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Wrong intent</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Price-zero intent — not a converting audience.</t>
         </is>
